--- a/pythonproject.xlsx
+++ b/pythonproject.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d60ad4f87f2bd4d2/Documents/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{1F1D8A4D-FA09-4C80-B75F-C58BA0DBB79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E978A704-A72A-4869-B51F-4F34C9F2E394}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{1F1D8A4D-FA09-4C80-B75F-C58BA0DBB79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4144446D-9DA9-48DA-927C-04E850588897}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="69">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -244,6 +244,9 @@
   </si>
   <si>
     <t>Excellent</t>
+  </si>
+  <si>
+    <t>Stressed</t>
   </si>
 </sst>
 </file>
@@ -3665,155 +3668,296 @@
       </c>
     </row>
     <row r="47" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="14"/>
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
+      <c r="A47" s="14">
+        <v>46288</v>
+      </c>
+      <c r="B47" s="10">
+        <v>300</v>
+      </c>
+      <c r="C47" s="10">
+        <v>30</v>
+      </c>
+      <c r="D47" s="10">
+        <v>270</v>
+      </c>
+      <c r="E47" s="10">
+        <v>110</v>
+      </c>
+      <c r="F47" s="10">
+        <v>450</v>
+      </c>
       <c r="G47" s="10"/>
       <c r="H47" s="10"/>
-      <c r="I47" s="15" t="str">
-        <f t="shared" ref="I46:I300" si="1">IF(SUM(B47:F47,H47)=0,"",SUM(B47:F47,H47))</f>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+      <c r="I47" s="15">
+        <f t="shared" ref="I47:I300" si="1">IF(SUM(B47:F47,H47)=0,"",SUM(B47:F47,H47))</f>
+        <v>1160</v>
+      </c>
+      <c r="J47" s="15">
+        <f t="shared" si="0"/>
+        <v>280</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="48" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="14"/>
-      <c r="B48" s="10"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
+      <c r="A48" s="14">
+        <v>46289</v>
+      </c>
+      <c r="B48" s="10">
+        <v>300</v>
+      </c>
+      <c r="C48" s="10">
+        <v>30</v>
+      </c>
+      <c r="D48" s="10">
+        <v>270</v>
+      </c>
+      <c r="E48" s="10">
+        <v>110</v>
+      </c>
+      <c r="F48" s="10">
+        <v>450</v>
+      </c>
       <c r="G48" s="10"/>
       <c r="H48" s="10"/>
-      <c r="I48" s="15"/>
-      <c r="J48" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
+      <c r="I48" s="15">
+        <v>1160</v>
+      </c>
+      <c r="J48" s="15">
+        <v>280</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="49" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="14"/>
-      <c r="B49" s="10"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
+      <c r="A49" s="14">
+        <v>46290</v>
+      </c>
+      <c r="B49" s="10">
+        <v>320</v>
+      </c>
+      <c r="C49" s="10">
+        <v>40</v>
+      </c>
+      <c r="D49" s="10">
+        <v>315</v>
+      </c>
+      <c r="E49" s="10">
+        <v>90</v>
+      </c>
+      <c r="F49" s="10">
+        <v>480</v>
+      </c>
       <c r="G49" s="10"/>
       <c r="H49" s="10"/>
-      <c r="I49" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
+      <c r="I49" s="15">
+        <f>IF(SUM(B49:F49,H49)=0,"",SUM(B49:F49,H49))</f>
+        <v>1245</v>
+      </c>
+      <c r="J49" s="15">
+        <f t="shared" si="0"/>
+        <v>195</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="50" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="14"/>
-      <c r="B50" s="10"/>
-      <c r="C50" s="10"/>
-      <c r="D50" s="10"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="10"/>
+      <c r="A50" s="14">
+        <v>46291</v>
+      </c>
+      <c r="B50" s="10">
+        <v>360</v>
+      </c>
+      <c r="C50" s="10">
+        <v>30</v>
+      </c>
+      <c r="D50" s="10">
+        <v>330</v>
+      </c>
+      <c r="E50" s="10">
+        <v>120</v>
+      </c>
+      <c r="F50" s="10">
+        <v>465</v>
+      </c>
       <c r="G50" s="10"/>
       <c r="H50" s="10"/>
-      <c r="I50" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
+      <c r="I50" s="15">
+        <f t="shared" si="1"/>
+        <v>1305</v>
+      </c>
+      <c r="J50" s="15">
+        <f t="shared" si="0"/>
+        <v>135</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="51" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="14"/>
-      <c r="B51" s="10"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
+      <c r="A51" s="14">
+        <v>46292</v>
+      </c>
+      <c r="B51" s="10">
+        <v>345</v>
+      </c>
+      <c r="C51" s="10">
+        <v>45</v>
+      </c>
+      <c r="D51" s="10">
+        <v>330</v>
+      </c>
+      <c r="E51" s="10">
+        <v>120</v>
+      </c>
+      <c r="F51" s="10">
+        <v>495</v>
+      </c>
       <c r="G51" s="10"/>
       <c r="H51" s="10"/>
-      <c r="I51" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
+      <c r="I51" s="15">
+        <f t="shared" si="1"/>
+        <v>1335</v>
+      </c>
+      <c r="J51" s="15">
+        <f t="shared" si="0"/>
+        <v>105</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="52" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="14"/>
-      <c r="B52" s="10"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="10"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="10"/>
+      <c r="A52" s="14">
+        <v>46293</v>
+      </c>
+      <c r="B52" s="10">
+        <v>420</v>
+      </c>
+      <c r="C52" s="10">
+        <v>0</v>
+      </c>
+      <c r="D52" s="10">
+        <v>400</v>
+      </c>
+      <c r="E52" s="10">
+        <v>120</v>
+      </c>
+      <c r="F52" s="10">
+        <v>120</v>
+      </c>
       <c r="G52" s="10"/>
       <c r="H52" s="10"/>
-      <c r="I52" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
+      <c r="I52" s="15">
+        <f t="shared" si="1"/>
+        <v>1060</v>
+      </c>
+      <c r="J52" s="15">
+        <f t="shared" si="0"/>
+        <v>380</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="53" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="14"/>
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
+      <c r="A53" s="14">
+        <v>46294</v>
+      </c>
+      <c r="B53" s="10">
+        <v>360</v>
+      </c>
+      <c r="C53" s="10">
+        <v>40</v>
+      </c>
+      <c r="D53" s="10">
+        <v>285</v>
+      </c>
+      <c r="E53" s="10">
+        <v>160</v>
+      </c>
+      <c r="F53" s="10">
+        <v>480</v>
+      </c>
       <c r="G53" s="10"/>
       <c r="H53" s="10"/>
-      <c r="I53" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
+      <c r="I53" s="15">
+        <f t="shared" si="1"/>
+        <v>1325</v>
+      </c>
+      <c r="J53" s="15">
+        <f t="shared" si="0"/>
+        <v>115</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="54" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="14"/>

--- a/pythonproject.xlsx
+++ b/pythonproject.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d60ad4f87f2bd4d2/Documents/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{1F1D8A4D-FA09-4C80-B75F-C58BA0DBB79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4144446D-9DA9-48DA-927C-04E850588897}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{1F1D8A4D-FA09-4C80-B75F-C58BA0DBB79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD15B970-C9FA-43F7-A0FE-B756A87E0225}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="69">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -3960,26 +3960,46 @@
       </c>
     </row>
     <row r="54" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="14"/>
-      <c r="B54" s="10"/>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
+      <c r="A54" s="14">
+        <v>46295</v>
+      </c>
+      <c r="B54" s="10">
+        <v>360</v>
+      </c>
+      <c r="C54" s="10">
+        <v>50</v>
+      </c>
+      <c r="D54" s="10">
+        <v>315</v>
+      </c>
+      <c r="E54" s="10">
+        <v>180</v>
+      </c>
+      <c r="F54" s="10">
+        <v>340</v>
+      </c>
       <c r="G54" s="10"/>
       <c r="H54" s="10"/>
-      <c r="I54" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
+      <c r="I54" s="15">
+        <f t="shared" si="1"/>
+        <v>1245</v>
+      </c>
+      <c r="J54" s="15">
+        <f t="shared" si="0"/>
+        <v>195</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="55" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="14"/>

--- a/pythonproject.xlsx
+++ b/pythonproject.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d60ad4f87f2bd4d2/Documents/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{1F1D8A4D-FA09-4C80-B75F-C58BA0DBB79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD15B970-C9FA-43F7-A0FE-B756A87E0225}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{1F1D8A4D-FA09-4C80-B75F-C58BA0DBB79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8832AAB-434B-4515-B2F1-1421D5BD49DE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="70">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -247,6 +247,9 @@
   </si>
   <si>
     <t>Stressed</t>
+  </si>
+  <si>
+    <t>only self study</t>
   </si>
 </sst>
 </file>
@@ -4002,48 +4005,88 @@
       </c>
     </row>
     <row r="55" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="14"/>
-      <c r="B55" s="10"/>
-      <c r="C55" s="10"/>
-      <c r="D55" s="10"/>
-      <c r="E55" s="10"/>
-      <c r="F55" s="10"/>
+      <c r="A55" s="14">
+        <v>46296</v>
+      </c>
+      <c r="B55" s="10">
+        <v>360</v>
+      </c>
+      <c r="C55" s="10">
+        <v>40</v>
+      </c>
+      <c r="D55" s="10">
+        <v>400</v>
+      </c>
+      <c r="E55" s="10">
+        <v>120</v>
+      </c>
+      <c r="F55" s="10">
+        <v>350</v>
+      </c>
       <c r="G55" s="10"/>
       <c r="H55" s="10"/>
-      <c r="I55" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
+      <c r="I55" s="15">
+        <f t="shared" si="1"/>
+        <v>1270</v>
+      </c>
+      <c r="J55" s="15">
+        <f t="shared" si="0"/>
+        <v>170</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="56" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="14"/>
-      <c r="B56" s="10"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="10"/>
-      <c r="E56" s="10"/>
-      <c r="F56" s="10"/>
+      <c r="A56" s="14">
+        <v>46297</v>
+      </c>
+      <c r="B56" s="10">
+        <v>300</v>
+      </c>
+      <c r="C56" s="10">
+        <v>50</v>
+      </c>
+      <c r="D56" s="10">
+        <v>420</v>
+      </c>
+      <c r="E56" s="10">
+        <v>160</v>
+      </c>
+      <c r="F56" s="10">
+        <v>360</v>
+      </c>
       <c r="G56" s="10"/>
       <c r="H56" s="10"/>
-      <c r="I56" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
+      <c r="I56" s="15">
+        <f t="shared" si="1"/>
+        <v>1290</v>
+      </c>
+      <c r="J56" s="15">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="57" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="14"/>

--- a/pythonproject.xlsx
+++ b/pythonproject.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d60ad4f87f2bd4d2/Documents/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{1F1D8A4D-FA09-4C80-B75F-C58BA0DBB79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8832AAB-434B-4515-B2F1-1421D5BD49DE}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="13_ncr:1_{1F1D8A4D-FA09-4C80-B75F-C58BA0DBB79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32B848B8-0C25-48B3-99B5-518B12B8F2D5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="70">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -4089,48 +4089,88 @@
       </c>
     </row>
     <row r="57" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="14"/>
-      <c r="B57" s="10"/>
-      <c r="C57" s="10"/>
-      <c r="D57" s="10"/>
-      <c r="E57" s="10"/>
-      <c r="F57" s="10"/>
+      <c r="A57" s="14">
+        <v>46298</v>
+      </c>
+      <c r="B57" s="10">
+        <v>360</v>
+      </c>
+      <c r="C57" s="10">
+        <v>30</v>
+      </c>
+      <c r="D57" s="10">
+        <v>450</v>
+      </c>
+      <c r="E57" s="10">
+        <v>220</v>
+      </c>
+      <c r="F57" s="10">
+        <v>300</v>
+      </c>
       <c r="G57" s="10"/>
       <c r="H57" s="10"/>
-      <c r="I57" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
+      <c r="I57" s="15">
+        <f t="shared" si="1"/>
+        <v>1360</v>
+      </c>
+      <c r="J57" s="15">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="58" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="14"/>
-      <c r="B58" s="10"/>
-      <c r="C58" s="10"/>
-      <c r="D58" s="10"/>
-      <c r="E58" s="10"/>
-      <c r="F58" s="10"/>
+      <c r="A58" s="14">
+        <v>46299</v>
+      </c>
+      <c r="B58" s="10">
+        <v>360</v>
+      </c>
+      <c r="C58" s="10">
+        <v>40</v>
+      </c>
+      <c r="D58" s="10">
+        <v>420</v>
+      </c>
+      <c r="E58" s="10">
+        <v>200</v>
+      </c>
+      <c r="F58" s="10">
+        <v>260</v>
+      </c>
       <c r="G58" s="10"/>
       <c r="H58" s="10"/>
-      <c r="I58" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
+      <c r="I58" s="15">
+        <f t="shared" si="1"/>
+        <v>1280</v>
+      </c>
+      <c r="J58" s="15">
+        <f t="shared" si="0"/>
+        <v>160</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="59" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="14"/>

--- a/pythonproject.xlsx
+++ b/pythonproject.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d60ad4f87f2bd4d2/Documents/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="13_ncr:1_{1F1D8A4D-FA09-4C80-B75F-C58BA0DBB79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32B848B8-0C25-48B3-99B5-518B12B8F2D5}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{1F1D8A4D-FA09-4C80-B75F-C58BA0DBB79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34154DD4-6097-43C7-AFD9-241756D3FC9B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="70">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -4173,26 +4173,46 @@
       </c>
     </row>
     <row r="59" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="14"/>
-      <c r="B59" s="10"/>
-      <c r="C59" s="10"/>
-      <c r="D59" s="10"/>
-      <c r="E59" s="10"/>
-      <c r="F59" s="10"/>
+      <c r="A59" s="14">
+        <v>46300</v>
+      </c>
+      <c r="B59" s="10">
+        <v>360</v>
+      </c>
+      <c r="C59" s="10">
+        <v>60</v>
+      </c>
+      <c r="D59" s="10">
+        <v>280</v>
+      </c>
+      <c r="E59" s="10">
+        <v>180</v>
+      </c>
+      <c r="F59" s="10">
+        <v>360</v>
+      </c>
       <c r="G59" s="10"/>
       <c r="H59" s="10"/>
-      <c r="I59" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="17"/>
+      <c r="I59" s="15">
+        <f t="shared" si="1"/>
+        <v>1240</v>
+      </c>
+      <c r="J59" s="15">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="60" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="14"/>

--- a/pythonproject.xlsx
+++ b/pythonproject.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d60ad4f87f2bd4d2/Documents/cap776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{1F1D8A4D-FA09-4C80-B75F-C58BA0DBB79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34154DD4-6097-43C7-AFD9-241756D3FC9B}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{1F1D8A4D-FA09-4C80-B75F-C58BA0DBB79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{757CAF12-40D0-4000-BD84-82E8AFBABE59}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="59">
   <si>
     <t>My Data, My Code — Daily Log</t>
   </si>
@@ -201,25 +201,10 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>Good</t>
-  </si>
-  <si>
-    <t>Satisfied</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
     <t>Productive day.</t>
   </si>
   <si>
-    <t>Neutral</t>
-  </si>
-  <si>
     <t>Classes and self-study completed.</t>
-  </si>
-  <si>
-    <t>High</t>
   </si>
   <si>
     <t>Regular college day.</t>
@@ -228,25 +213,7 @@
     <t>Completed study and coding.</t>
   </si>
   <si>
-    <t>Very Satisfied</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>Unsatisfied</t>
-  </si>
-  <si>
     <t>Normal day with some study and coding.</t>
-  </si>
-  <si>
-    <t>Very Unsatisfied</t>
-  </si>
-  <si>
-    <t>Excellent</t>
-  </si>
-  <si>
-    <t>Stressed</t>
   </si>
   <si>
     <t>only self study</t>
@@ -2059,13 +2026,17 @@
       <c r="J6" s="15">
         <v>220</v>
       </c>
-      <c r="K6" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
+      <c r="K6" s="16">
+        <v>4</v>
+      </c>
+      <c r="L6" s="16">
+        <v>3.5</v>
+      </c>
+      <c r="M6" s="16">
+        <v>3</v>
+      </c>
       <c r="N6" s="17" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2095,17 +2066,17 @@
       <c r="J7" s="15">
         <v>230</v>
       </c>
-      <c r="K7" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="L7" s="16" t="s">
+      <c r="K7" s="16">
+        <v>3</v>
+      </c>
+      <c r="L7" s="16">
+        <v>4</v>
+      </c>
+      <c r="M7" s="16">
+        <v>4.5</v>
+      </c>
+      <c r="N7" s="17" t="s">
         <v>54</v>
-      </c>
-      <c r="M7" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2135,17 +2106,17 @@
       <c r="J8" s="15">
         <v>215</v>
       </c>
-      <c r="K8" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="L8" s="16" t="s">
+      <c r="K8" s="16">
+        <v>5</v>
+      </c>
+      <c r="L8" s="16">
+        <v>5</v>
+      </c>
+      <c r="M8" s="16">
+        <v>4</v>
+      </c>
+      <c r="N8" s="17" t="s">
         <v>54</v>
-      </c>
-      <c r="M8" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N8" s="17" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2175,17 +2146,17 @@
       <c r="J9" s="15">
         <v>215</v>
       </c>
-      <c r="K9" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="L9" s="16" t="s">
+      <c r="K9" s="16">
+        <v>4</v>
+      </c>
+      <c r="L9" s="16">
+        <v>3</v>
+      </c>
+      <c r="M9" s="16">
+        <v>4</v>
+      </c>
+      <c r="N9" s="17" t="s">
         <v>54</v>
-      </c>
-      <c r="M9" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:14" s="22" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2215,17 +2186,17 @@
       <c r="J10" s="24">
         <v>225</v>
       </c>
-      <c r="K10" s="20" t="s">
+      <c r="K10" s="20">
+        <v>3</v>
+      </c>
+      <c r="L10" s="20">
+        <v>4</v>
+      </c>
+      <c r="M10" s="20">
+        <v>5</v>
+      </c>
+      <c r="N10" s="21" t="s">
         <v>53</v>
-      </c>
-      <c r="L10" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="M10" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="N10" s="21" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2255,17 +2226,17 @@
       <c r="J11" s="11">
         <v>235</v>
       </c>
-      <c r="K11" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="L11" s="12" t="s">
+      <c r="K11" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="L11" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="M11" s="12">
+        <v>3</v>
+      </c>
+      <c r="N11" s="13" t="s">
         <v>54</v>
-      </c>
-      <c r="M11" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="N11" s="13" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2295,17 +2266,17 @@
       <c r="J12" s="11">
         <v>245</v>
       </c>
-      <c r="K12" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="L12" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="M12" s="12" t="s">
-        <v>59</v>
+      <c r="K12" s="12">
+        <v>5</v>
+      </c>
+      <c r="L12" s="12">
+        <v>3</v>
+      </c>
+      <c r="M12" s="12">
+        <v>4.5</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2335,17 +2306,17 @@
       <c r="J13" s="11">
         <v>130</v>
       </c>
-      <c r="K13" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L13" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="M13" s="12" t="s">
-        <v>59</v>
+      <c r="K13" s="12">
+        <v>3</v>
+      </c>
+      <c r="L13" s="12">
+        <v>4</v>
+      </c>
+      <c r="M13" s="12">
+        <v>5</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2375,17 +2346,17 @@
       <c r="J14" s="11">
         <v>215</v>
       </c>
-      <c r="K14" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L14" s="12" t="s">
+      <c r="K14" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="L14" s="12">
+        <v>3</v>
+      </c>
+      <c r="M14" s="12">
+        <v>5</v>
+      </c>
+      <c r="N14" s="13" t="s">
         <v>54</v>
-      </c>
-      <c r="M14" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="N14" s="13" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2415,17 +2386,17 @@
       <c r="J15" s="11">
         <v>220</v>
       </c>
-      <c r="K15" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L15" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="M15" s="12" t="s">
-        <v>55</v>
+      <c r="K15" s="12">
+        <v>5</v>
+      </c>
+      <c r="L15" s="12">
+        <v>5</v>
+      </c>
+      <c r="M15" s="12">
+        <v>3</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2455,17 +2426,17 @@
       <c r="J16" s="11">
         <v>170</v>
       </c>
-      <c r="K16" s="12" t="s">
+      <c r="K16" s="12">
+        <v>4</v>
+      </c>
+      <c r="L16" s="12">
+        <v>2</v>
+      </c>
+      <c r="M16" s="12">
+        <v>4</v>
+      </c>
+      <c r="N16" s="13" t="s">
         <v>53</v>
-      </c>
-      <c r="L16" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="M16" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="N16" s="13" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2495,17 +2466,17 @@
       <c r="J17" s="11">
         <v>160</v>
       </c>
-      <c r="K17" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L17" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="M17" s="12" t="s">
-        <v>59</v>
+      <c r="K17" s="12">
+        <v>4</v>
+      </c>
+      <c r="L17" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="M17" s="12">
+        <v>4</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2535,17 +2506,17 @@
       <c r="J18" s="11">
         <v>205</v>
       </c>
-      <c r="K18" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L18" s="12" t="s">
+      <c r="K18" s="12">
+        <v>4</v>
+      </c>
+      <c r="L18" s="12">
+        <v>4</v>
+      </c>
+      <c r="M18" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="N18" s="13" t="s">
         <v>54</v>
-      </c>
-      <c r="M18" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="N18" s="13" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2575,17 +2546,17 @@
       <c r="J19" s="11">
         <v>185</v>
       </c>
-      <c r="K19" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="L19" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="M19" s="12" t="s">
-        <v>55</v>
+      <c r="K19" s="12">
+        <v>5</v>
+      </c>
+      <c r="L19" s="12">
+        <v>5</v>
+      </c>
+      <c r="M19" s="12">
+        <v>5</v>
       </c>
       <c r="N19" s="13" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2615,17 +2586,17 @@
       <c r="J20" s="11">
         <v>125</v>
       </c>
-      <c r="K20" s="12" t="s">
+      <c r="K20" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="L20" s="12">
+        <v>4</v>
+      </c>
+      <c r="M20" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="N20" s="13" t="s">
         <v>53</v>
-      </c>
-      <c r="L20" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="M20" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="N20" s="13" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2655,17 +2626,17 @@
       <c r="J21" s="11">
         <v>135</v>
       </c>
-      <c r="K21" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="L21" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="M21" s="12" t="s">
-        <v>55</v>
+      <c r="K21" s="12">
+        <v>3</v>
+      </c>
+      <c r="L21" s="12">
+        <v>3</v>
+      </c>
+      <c r="M21" s="12">
+        <v>5</v>
       </c>
       <c r="N21" s="13" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2695,17 +2666,17 @@
       <c r="J22" s="11">
         <v>95</v>
       </c>
-      <c r="K22" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L22" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="M22" s="12" t="s">
-        <v>63</v>
+      <c r="K22" s="12">
+        <v>4</v>
+      </c>
+      <c r="L22" s="12">
+        <v>5</v>
+      </c>
+      <c r="M22" s="12">
+        <v>4.5</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2735,17 +2706,17 @@
       <c r="J23" s="11">
         <v>200</v>
       </c>
-      <c r="K23" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="L23" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="M23" s="12" t="s">
-        <v>63</v>
+      <c r="K23" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="L23" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="M23" s="12">
+        <v>4</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2775,17 +2746,17 @@
       <c r="J24" s="11">
         <v>235</v>
       </c>
-      <c r="K24" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L24" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="M24" s="12" t="s">
+      <c r="K24" s="12">
+        <v>4</v>
+      </c>
+      <c r="L24" s="12">
+        <v>4</v>
+      </c>
+      <c r="M24" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="N24" s="13" t="s">
         <v>55</v>
-      </c>
-      <c r="N24" s="13" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2815,17 +2786,17 @@
       <c r="J25" s="11">
         <v>100</v>
       </c>
-      <c r="K25" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L25" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="M25" s="12" t="s">
-        <v>55</v>
+      <c r="K25" s="12">
+        <v>4</v>
+      </c>
+      <c r="L25" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="M25" s="12">
+        <v>4</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2855,17 +2826,17 @@
       <c r="J26" s="11">
         <v>170</v>
       </c>
-      <c r="K26" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L26" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="M26" s="12" t="s">
-        <v>55</v>
+      <c r="K26" s="12">
+        <v>4</v>
+      </c>
+      <c r="L26" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="M26" s="12">
+        <v>5</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2895,17 +2866,17 @@
       <c r="J27" s="11">
         <v>255</v>
       </c>
-      <c r="K27" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L27" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="M27" s="12" t="s">
-        <v>55</v>
+      <c r="K27" s="12">
+        <v>4</v>
+      </c>
+      <c r="L27" s="12">
+        <v>4</v>
+      </c>
+      <c r="M27" s="12">
+        <v>5</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2935,17 +2906,17 @@
       <c r="J28" s="11">
         <v>155</v>
       </c>
-      <c r="K28" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L28" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="M28" s="12" t="s">
-        <v>59</v>
+      <c r="K28" s="12">
+        <v>4</v>
+      </c>
+      <c r="L28" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="M28" s="12">
+        <v>5</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2975,17 +2946,17 @@
       <c r="J29" s="11">
         <v>185</v>
       </c>
-      <c r="K29" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L29" s="12" t="s">
+      <c r="K29" s="12">
+        <v>4</v>
+      </c>
+      <c r="L29" s="12">
+        <v>4</v>
+      </c>
+      <c r="M29" s="12">
+        <v>5</v>
+      </c>
+      <c r="N29" s="13" t="s">
         <v>57</v>
-      </c>
-      <c r="M29" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="N29" s="13" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3015,17 +2986,17 @@
       <c r="J30" s="11">
         <v>220</v>
       </c>
-      <c r="K30" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L30" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="M30" s="12" t="s">
-        <v>55</v>
+      <c r="K30" s="12">
+        <v>5</v>
+      </c>
+      <c r="L30" s="12">
+        <v>5</v>
+      </c>
+      <c r="M30" s="12">
+        <v>4</v>
       </c>
       <c r="N30" s="13" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3055,17 +3026,17 @@
       <c r="J31" s="11">
         <v>285</v>
       </c>
-      <c r="K31" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L31" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="M31" s="12" t="s">
-        <v>55</v>
+      <c r="K31" s="12">
+        <v>3</v>
+      </c>
+      <c r="L31" s="12">
+        <v>3</v>
+      </c>
+      <c r="M31" s="12">
+        <v>5</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3095,17 +3066,17 @@
       <c r="J32" s="11">
         <v>105</v>
       </c>
-      <c r="K32" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L32" s="12" t="s">
+      <c r="K32" s="12">
+        <v>3.4</v>
+      </c>
+      <c r="L32" s="12">
+        <v>4</v>
+      </c>
+      <c r="M32" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="N32" s="13" t="s">
         <v>54</v>
-      </c>
-      <c r="M32" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="N32" s="13" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3135,17 +3106,17 @@
       <c r="J33" s="11">
         <v>170</v>
       </c>
-      <c r="K33" s="12" t="s">
+      <c r="K33" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="L33" s="12">
+        <v>5</v>
+      </c>
+      <c r="M33" s="12">
+        <v>3</v>
+      </c>
+      <c r="N33" s="13" t="s">
         <v>53</v>
-      </c>
-      <c r="L33" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="M33" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="N33" s="13" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3175,17 +3146,17 @@
       <c r="J34" s="11">
         <v>155</v>
       </c>
-      <c r="K34" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L34" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="M34" s="12" t="s">
-        <v>55</v>
+      <c r="K34" s="12">
+        <v>4</v>
+      </c>
+      <c r="L34" s="12">
+        <v>3</v>
+      </c>
+      <c r="M34" s="12">
+        <v>4</v>
       </c>
       <c r="N34" s="13" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3215,17 +3186,17 @@
       <c r="J35" s="11">
         <v>200</v>
       </c>
-      <c r="K35" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="L35" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="M35" s="12" t="s">
+      <c r="K35" s="12">
+        <v>5</v>
+      </c>
+      <c r="L35" s="12">
+        <v>4</v>
+      </c>
+      <c r="M35" s="12">
+        <v>5</v>
+      </c>
+      <c r="N35" s="13" t="s">
         <v>55</v>
-      </c>
-      <c r="N35" s="13" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3255,17 +3226,17 @@
       <c r="J36" s="11">
         <v>220</v>
       </c>
-      <c r="K36" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L36" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="M36" s="12" t="s">
-        <v>55</v>
+      <c r="K36" s="12">
+        <v>4</v>
+      </c>
+      <c r="L36" s="12">
+        <v>3</v>
+      </c>
+      <c r="M36" s="12">
+        <v>4</v>
       </c>
       <c r="N36" s="13" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3295,17 +3266,17 @@
       <c r="J37" s="11">
         <v>250</v>
       </c>
-      <c r="K37" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L37" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="M37" s="12" t="s">
-        <v>55</v>
+      <c r="K37" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="L37" s="12">
+        <v>4</v>
+      </c>
+      <c r="M37" s="12">
+        <v>5</v>
       </c>
       <c r="N37" s="13" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3335,17 +3306,17 @@
       <c r="J38" s="11">
         <v>235</v>
       </c>
-      <c r="K38" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L38" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="M38" s="12" t="s">
-        <v>59</v>
+      <c r="K38" s="12">
+        <v>3</v>
+      </c>
+      <c r="L38" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="M38" s="12">
+        <v>3.5</v>
       </c>
       <c r="N38" s="13" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3375,17 +3346,17 @@
       <c r="J39" s="11">
         <v>190</v>
       </c>
-      <c r="K39" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L39" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="M39" s="12" t="s">
+      <c r="K39" s="12">
+        <v>4</v>
+      </c>
+      <c r="L39" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="M39" s="12">
+        <v>4</v>
+      </c>
+      <c r="N39" s="13" t="s">
         <v>55</v>
-      </c>
-      <c r="N39" s="13" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3415,17 +3386,17 @@
       <c r="J40" s="11">
         <v>230</v>
       </c>
-      <c r="K40" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L40" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="M40" s="12" t="s">
-        <v>55</v>
+      <c r="K40" s="12">
+        <v>5</v>
+      </c>
+      <c r="L40" s="12">
+        <v>4</v>
+      </c>
+      <c r="M40" s="12">
+        <v>4.5</v>
       </c>
       <c r="N40" s="13" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3455,17 +3426,17 @@
       <c r="J41" s="11">
         <v>205</v>
       </c>
-      <c r="K41" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L41" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="M41" s="12" t="s">
+      <c r="K41" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="L41" s="12">
+        <v>5</v>
+      </c>
+      <c r="M41" s="12">
+        <v>4</v>
+      </c>
+      <c r="N41" s="13" t="s">
         <v>55</v>
-      </c>
-      <c r="N41" s="13" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3495,17 +3466,17 @@
       <c r="J42" s="11">
         <v>170</v>
       </c>
-      <c r="K42" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L42" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="M42" s="12" t="s">
-        <v>55</v>
+      <c r="K42" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="L42" s="12">
+        <v>5</v>
+      </c>
+      <c r="M42" s="12">
+        <v>4</v>
       </c>
       <c r="N42" s="13" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3535,17 +3506,17 @@
       <c r="J43" s="11">
         <v>230</v>
       </c>
-      <c r="K43" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L43" s="12" t="s">
+      <c r="K43" s="12">
+        <v>3</v>
+      </c>
+      <c r="L43" s="12">
+        <v>5</v>
+      </c>
+      <c r="M43" s="12">
+        <v>3</v>
+      </c>
+      <c r="N43" s="13" t="s">
         <v>54</v>
-      </c>
-      <c r="M43" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="N43" s="13" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3575,17 +3546,17 @@
       <c r="J44" s="11">
         <v>205</v>
       </c>
-      <c r="K44" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L44" s="12" t="s">
+      <c r="K44" s="12">
+        <v>4</v>
+      </c>
+      <c r="L44" s="12">
+        <v>4</v>
+      </c>
+      <c r="M44" s="12">
+        <v>4</v>
+      </c>
+      <c r="N44" s="13" t="s">
         <v>54</v>
-      </c>
-      <c r="M44" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="N44" s="13" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3615,17 +3586,17 @@
       <c r="J45" s="11">
         <v>130</v>
       </c>
-      <c r="K45" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L45" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="M45" s="12" t="s">
-        <v>59</v>
+      <c r="K45" s="12">
+        <v>5</v>
+      </c>
+      <c r="L45" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="M45" s="12">
+        <v>5</v>
       </c>
       <c r="N45" s="13" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3657,17 +3628,17 @@
         <f t="shared" ref="J46:J300" si="0">IF(I46="","",1440-I46)</f>
         <v>215</v>
       </c>
-      <c r="K46" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L46" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="M46" s="16" t="s">
-        <v>63</v>
+      <c r="K46" s="16">
+        <v>4</v>
+      </c>
+      <c r="L46" s="16">
+        <v>3</v>
+      </c>
+      <c r="M46" s="16">
+        <v>4</v>
       </c>
       <c r="N46" s="17" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3699,17 +3670,17 @@
         <f t="shared" si="0"/>
         <v>280</v>
       </c>
-      <c r="K47" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="L47" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="M47" s="16" t="s">
-        <v>55</v>
+      <c r="K47" s="16">
+        <v>3</v>
+      </c>
+      <c r="L47" s="16">
+        <v>3.5</v>
+      </c>
+      <c r="M47" s="16">
+        <v>5</v>
       </c>
       <c r="N47" s="17" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3739,17 +3710,17 @@
       <c r="J48" s="15">
         <v>280</v>
       </c>
-      <c r="K48" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="L48" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M48" s="16" t="s">
-        <v>59</v>
+      <c r="K48" s="16">
+        <v>4</v>
+      </c>
+      <c r="L48" s="16">
+        <v>4</v>
+      </c>
+      <c r="M48" s="16">
+        <v>5</v>
       </c>
       <c r="N48" s="17" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3781,17 +3752,17 @@
         <f t="shared" si="0"/>
         <v>195</v>
       </c>
-      <c r="K49" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L49" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="M49" s="16" t="s">
-        <v>55</v>
+      <c r="K49" s="16">
+        <v>4</v>
+      </c>
+      <c r="L49" s="16">
+        <v>5</v>
+      </c>
+      <c r="M49" s="16">
+        <v>4.5</v>
       </c>
       <c r="N49" s="17" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3823,17 +3794,17 @@
         <f t="shared" si="0"/>
         <v>135</v>
       </c>
-      <c r="K50" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="L50" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="M50" s="16" t="s">
-        <v>59</v>
+      <c r="K50" s="16">
+        <v>4.5</v>
+      </c>
+      <c r="L50" s="16">
+        <v>3.5</v>
+      </c>
+      <c r="M50" s="16">
+        <v>4</v>
       </c>
       <c r="N50" s="17" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3865,17 +3836,17 @@
         <f t="shared" si="0"/>
         <v>105</v>
       </c>
-      <c r="K51" s="16" t="s">
+      <c r="K51" s="16">
+        <v>4.5</v>
+      </c>
+      <c r="L51" s="16">
+        <v>3</v>
+      </c>
+      <c r="M51" s="16">
+        <v>5</v>
+      </c>
+      <c r="N51" s="17" t="s">
         <v>53</v>
-      </c>
-      <c r="L51" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="M51" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N51" s="17" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3907,17 +3878,17 @@
         <f t="shared" si="0"/>
         <v>380</v>
       </c>
-      <c r="K52" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="L52" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="M52" s="16" t="s">
-        <v>59</v>
+      <c r="K52" s="16">
+        <v>5</v>
+      </c>
+      <c r="L52" s="16">
+        <v>4.5</v>
+      </c>
+      <c r="M52" s="16">
+        <v>4</v>
       </c>
       <c r="N52" s="17" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="53" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3949,17 +3920,17 @@
         <f t="shared" si="0"/>
         <v>115</v>
       </c>
-      <c r="K53" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="L53" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M53" s="16" t="s">
-        <v>55</v>
+      <c r="K53" s="16">
+        <v>5</v>
+      </c>
+      <c r="L53" s="16">
+        <v>5</v>
+      </c>
+      <c r="M53" s="16">
+        <v>3.4</v>
       </c>
       <c r="N53" s="17" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3991,17 +3962,17 @@
         <f t="shared" si="0"/>
         <v>195</v>
       </c>
-      <c r="K54" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L54" s="16" t="s">
+      <c r="K54" s="16">
+        <v>3</v>
+      </c>
+      <c r="L54" s="16">
+        <v>4</v>
+      </c>
+      <c r="M54" s="16">
+        <v>5</v>
+      </c>
+      <c r="N54" s="17" t="s">
         <v>54</v>
-      </c>
-      <c r="M54" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="N54" s="17" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -4033,17 +4004,17 @@
         <f t="shared" si="0"/>
         <v>170</v>
       </c>
-      <c r="K55" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L55" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="M55" s="16" t="s">
-        <v>63</v>
+      <c r="K55" s="16">
+        <v>3</v>
+      </c>
+      <c r="L55" s="16">
+        <v>4</v>
+      </c>
+      <c r="M55" s="16">
+        <v>3.5</v>
       </c>
       <c r="N55" s="17" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -4075,17 +4046,17 @@
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-      <c r="K56" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="L56" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="M56" s="16" t="s">
-        <v>55</v>
+      <c r="K56" s="16">
+        <v>2</v>
+      </c>
+      <c r="L56" s="16">
+        <v>5</v>
+      </c>
+      <c r="M56" s="16">
+        <v>4.5</v>
       </c>
       <c r="N56" s="17" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="57" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -4117,17 +4088,17 @@
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="K57" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L57" s="16" t="s">
+      <c r="K57" s="16">
+        <v>4</v>
+      </c>
+      <c r="L57" s="16">
+        <v>4.5</v>
+      </c>
+      <c r="M57" s="16">
+        <v>3</v>
+      </c>
+      <c r="N57" s="17" t="s">
         <v>54</v>
-      </c>
-      <c r="M57" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="N57" s="17" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="58" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -4159,17 +4130,17 @@
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
-      <c r="K58" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L58" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="M58" s="16" t="s">
-        <v>59</v>
+      <c r="K58" s="16">
+        <v>4.5</v>
+      </c>
+      <c r="L58" s="16">
+        <v>5</v>
+      </c>
+      <c r="M58" s="16">
+        <v>4</v>
       </c>
       <c r="N58" s="17" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="59" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -4201,17 +4172,17 @@
         <f t="shared" si="0"/>
         <v>200</v>
       </c>
-      <c r="K59" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="L59" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="M59" s="16" t="s">
-        <v>55</v>
+      <c r="K59" s="16">
+        <v>5</v>
+      </c>
+      <c r="L59" s="16">
+        <v>4</v>
+      </c>
+      <c r="M59" s="16">
+        <v>4.5</v>
       </c>
       <c r="N59" s="17" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
